--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3439,10 +3439,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120899831</v>
+        <v>120897287</v>
       </c>
       <c r="B24" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3486,14 +3486,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Grävlingskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561463</v>
+        <v>561386</v>
       </c>
       <c r="R24" t="n">
-        <v>6630396</v>
+        <v>6630526</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3523,9 +3523,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3545,7 +3555,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Tallhällmark</t>
+          <t>Tall/gran hällmark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3563,10 +3573,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120897287</v>
+        <v>120899831</v>
       </c>
       <c r="B25" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3598,7 +3608,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3610,14 +3620,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grävlingskogen, Ramnäs, Vstm</t>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561386</v>
+        <v>561463</v>
       </c>
       <c r="R25" t="n">
-        <v>6630526</v>
+        <v>6630396</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3647,19 +3657,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Tall/gran hällmark</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3700,7 +3700,7 @@
         <v>121115102</v>
       </c>
       <c r="B26" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>121114354</v>
       </c>
       <c r="B27" t="n">
-        <v>91998</v>
+        <v>92008</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3952,7 +3952,7 @@
         <v>120901658</v>
       </c>
       <c r="B28" t="n">
-        <v>56560</v>
+        <v>56563</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3439,7 +3439,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120897287</v>
+        <v>120899831</v>
       </c>
       <c r="B24" t="n">
         <v>92008</v>
@@ -3474,7 +3474,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3486,14 +3486,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grävlingskogen, Ramnäs, Vstm</t>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561386</v>
+        <v>561463</v>
       </c>
       <c r="R24" t="n">
-        <v>6630526</v>
+        <v>6630396</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3523,19 +3523,9 @@
           <t>2024-11-05</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>12:58</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:58</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3555,7 +3545,7 @@
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Tall/gran hällmark</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3573,7 +3563,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120899831</v>
+        <v>120897287</v>
       </c>
       <c r="B25" t="n">
         <v>92008</v>
@@ -3608,7 +3598,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3620,14 +3610,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Grävlingskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561463</v>
+        <v>561386</v>
       </c>
       <c r="R25" t="n">
-        <v>6630396</v>
+        <v>6630526</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3657,9 +3647,19 @@
           <t>2024-11-05</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>12:58</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Tallhällmark</t>
+          <t>Tall/gran hällmark</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3697,10 +3697,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121115102</v>
+        <v>121114354</v>
       </c>
       <c r="B26" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Grävlingskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsskogen, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561395</v>
+        <v>561426</v>
       </c>
       <c r="R26" t="n">
-        <v>6630537</v>
+        <v>6630572</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121114354</v>
+        <v>121115102</v>
       </c>
       <c r="B27" t="n">
-        <v>92008</v>
+        <v>92020</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3868,14 +3868,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Acktjärnsskogen, Grävlingskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561426</v>
+        <v>561395</v>
       </c>
       <c r="R27" t="n">
-        <v>6630572</v>
+        <v>6630537</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3700,7 +3700,7 @@
         <v>121114354</v>
       </c>
       <c r="B26" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3826,7 +3826,7 @@
         <v>121115102</v>
       </c>
       <c r="B27" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3697,10 +3697,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121114354</v>
+        <v>121115102</v>
       </c>
       <c r="B26" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3742,14 +3742,14 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Acktjärnsskogen, Grävlingskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561426</v>
+        <v>561395</v>
       </c>
       <c r="R26" t="n">
-        <v>6630572</v>
+        <v>6630537</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3791,7 +3791,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3823,10 +3823,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121115102</v>
+        <v>121114354</v>
       </c>
       <c r="B27" t="n">
-        <v>92021</v>
+        <v>92024</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3868,14 +3868,14 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Grävlingskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsskogen, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561395</v>
+        <v>561426</v>
       </c>
       <c r="R27" t="n">
-        <v>6630537</v>
+        <v>6630572</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3917,7 +3917,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3952,7 +3952,7 @@
         <v>120901658</v>
       </c>
       <c r="B28" t="n">
-        <v>56563</v>
+        <v>56566</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3952,7 +3952,7 @@
         <v>120901658</v>
       </c>
       <c r="B28" t="n">
-        <v>56566</v>
+        <v>56567</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -3952,7 +3952,7 @@
         <v>120901658</v>
       </c>
       <c r="B28" t="n">
-        <v>56567</v>
+        <v>56568</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4080,6 +4080,115 @@
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127763280</v>
+      </c>
+      <c r="B29" t="n">
+        <v>92614</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4361</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Orange taggsvamp</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hydnellum aurantiacum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>561378</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6630614</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92614</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>92623</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92623</v>
+        <v>92631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92631</v>
+        <v>92632</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92632</v>
+        <v>92633</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92633</v>
+        <v>92634</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92634</v>
+        <v>92642</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4085,7 +4085,7 @@
         <v>127763280</v>
       </c>
       <c r="B29" t="n">
-        <v>92642</v>
+        <v>92734</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4189,6 +4189,262 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131081947</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58043</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131081201</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57725</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4194,7 +4194,7 @@
         <v>131081947</v>
       </c>
       <c r="B30" t="n">
-        <v>58043</v>
+        <v>58045</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>131081201</v>
       </c>
       <c r="B31" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4194,7 +4194,7 @@
         <v>131081947</v>
       </c>
       <c r="B30" t="n">
-        <v>58045</v>
+        <v>58046</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>131081201</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>57728</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4194,7 +4194,7 @@
         <v>131081947</v>
       </c>
       <c r="B30" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>131081201</v>
       </c>
       <c r="B31" t="n">
-        <v>57728</v>
+        <v>57729</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4194,7 +4194,7 @@
         <v>131081947</v>
       </c>
       <c r="B30" t="n">
-        <v>58047</v>
+        <v>58050</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>131081201</v>
       </c>
       <c r="B31" t="n">
-        <v>57729</v>
+        <v>57732</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4194,7 +4194,7 @@
         <v>131081947</v>
       </c>
       <c r="B30" t="n">
-        <v>58050</v>
+        <v>58051</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4322,7 +4322,7 @@
         <v>131081201</v>
       </c>
       <c r="B31" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4583,7 +4583,7 @@
         <v>131678761</v>
       </c>
       <c r="B33" t="n">
-        <v>58075</v>
+        <v>58077</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AY40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5341,6 +5341,231 @@
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>132477434</v>
+      </c>
+      <c r="B39" t="n">
+        <v>91855</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>561397</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6630622</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="inlineStr"/>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>132477950</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>561288</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6630451</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4976,7 +4976,7 @@
         <v>131883389</v>
       </c>
       <c r="B36" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131881710</v>
       </c>
       <c r="B37" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>131883208</v>
       </c>
       <c r="B38" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>132477434</v>
       </c>
       <c r="B39" t="n">
-        <v>91855</v>
+        <v>91861</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>132477950</v>
       </c>
       <c r="B40" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -4976,7 +4976,7 @@
         <v>131883389</v>
       </c>
       <c r="B36" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>131881710</v>
       </c>
       <c r="B37" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
         <v>131883208</v>
       </c>
       <c r="B38" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>132477434</v>
       </c>
       <c r="B39" t="n">
-        <v>91861</v>
+        <v>91871</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>132477950</v>
       </c>
       <c r="B40" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -5346,7 +5346,7 @@
         <v>132477434</v>
       </c>
       <c r="B39" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -5346,7 +5346,7 @@
         <v>132477434</v>
       </c>
       <c r="B39" t="n">
-        <v>91872</v>
+        <v>91873</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5457,7 +5457,7 @@
         <v>132477950</v>
       </c>
       <c r="B40" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -5346,7 +5346,7 @@
         <v>132477434</v>
       </c>
       <c r="B39" t="n">
-        <v>91873</v>
+        <v>91875</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -5346,7 +5346,7 @@
         <v>132477434</v>
       </c>
       <c r="B39" t="n">
-        <v>91875</v>
+        <v>91876</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY40"/>
+  <dimension ref="A1:AY65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1677130</v>
+        <v>132477399</v>
       </c>
       <c r="B2" t="n">
-        <v>89355</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>3008</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Timmerticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Amyloporia sinuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Rajchenb. &amp; al.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>561350.9857018556</v>
+        <v>561339</v>
       </c>
       <c r="R2" t="n">
-        <v>6630478.80400019</v>
+        <v>6630330</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2009-09-17</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2009-09-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,17 +757,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Barrblandskog, hällmarker</t>
+          <t>Gammal barrblandskog</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -797,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>68993358</v>
+        <v>103261064</v>
       </c>
       <c r="B3" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92632</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,39 +797,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561339.1745940452</v>
+        <v>561428</v>
       </c>
       <c r="R3" t="n">
-        <v>6630339.219684619</v>
+        <v>6630643</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -869,22 +854,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-01-07</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-01-07</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -897,30 +872,35 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Granskog, dikad</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Gran</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>68993369</v>
+        <v>127763280</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,39 +908,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>4361</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Batsch:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>561339.1745940452</v>
+        <v>561378</v>
       </c>
       <c r="R4" t="n">
-        <v>6630339.219684619</v>
+        <v>6630614</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,27 +973,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-01-07</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-01-07</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>tall</t>
+          <t>2025-08-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,33 +987,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Ralf Lundmark</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>68993357</v>
+        <v>68993358</v>
       </c>
       <c r="B5" t="n">
-        <v>90676</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,21 +1017,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1073,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561339.1745940452</v>
+        <v>561339</v>
       </c>
       <c r="R5" t="n">
-        <v>6630339.219684619</v>
+        <v>6630339</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1106,19 +1076,9 @@
           <t>2018-01-07</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-01-07</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1146,55 +1106,56 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89542211</v>
+        <v>95741056</v>
       </c>
       <c r="B6" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>561434.7063614886</v>
+        <v>561345</v>
       </c>
       <c r="R6" t="n">
-        <v>6630445.465214299</v>
+        <v>6630284</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,27 +1182,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>inventering för Lst</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,43 +1196,34 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>torrgran</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>89542208</v>
+        <v>95741054</v>
       </c>
       <c r="B7" t="n">
-        <v>4941</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,39 +1231,45 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>105212</v>
+        <v>4366</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Barrpraktbagge</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chrysobothris chrysostigma</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561320.5970350681</v>
+        <v>561350</v>
       </c>
       <c r="R7" t="n">
-        <v>6630426.472598304</v>
+        <v>6630303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,27 +1296,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-08-25</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>inventering för Lst</t>
+          <t>1 fruktkropp</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1382,43 +1315,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>bruten solexponerad granstam</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>89542209</v>
+        <v>103261122</v>
       </c>
       <c r="B8" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1426,39 +1350,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>4379</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561331.9626640952</v>
+        <v>561482</v>
       </c>
       <c r="R8" t="n">
-        <v>6630562.523898256</v>
+        <v>6630524</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1485,27 +1407,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>inventering för Lst</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1514,43 +1421,34 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>torrtall</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>89542206</v>
+        <v>103261193</v>
       </c>
       <c r="B9" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89085</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,39 +1456,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>4379</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>561354.1327046107</v>
+        <v>561381</v>
       </c>
       <c r="R9" t="n">
-        <v>6630379.723879261</v>
+        <v>6630294</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1617,27 +1513,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>inventering för Lst</t>
+          <t>2022-08-29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1646,86 +1527,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>grov torraka</t>
+          <t>Skogsbilväg</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>89542203</v>
+        <v>1282521</v>
       </c>
       <c r="B10" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89138</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>4404</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Sotvaxskivling</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hygrophorus camarophyllus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Alb. &amp; Schwein.) Dumée &amp; al.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>561346.0495131966</v>
+        <v>561351</v>
       </c>
       <c r="R10" t="n">
-        <v>6630319.707448714</v>
+        <v>6630479</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1749,27 +1616,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>inventering för Lst</t>
+          <t>2009-09-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1783,38 +1635,28 @@
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>nydöd tall</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>89542212</v>
+        <v>1677130</v>
       </c>
       <c r="B11" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1822,42 +1664,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>561434.7063614886</v>
+        <v>561351</v>
       </c>
       <c r="R11" t="n">
-        <v>6630445.465214299</v>
+        <v>6630479</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1881,27 +1718,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2009-09-17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>inventering för Lst</t>
+          <t>2009-09-17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1915,82 +1737,71 @@
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
+          <t>Barrblandskog, hällmarker</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>torrgran</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>89542200</v>
+        <v>112708997</v>
       </c>
       <c r="B12" t="n">
-        <v>9009</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>101603</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Furustumpbagge</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Plegaderus saucius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Erichson, 1834</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>N om Stora Acktjärnen, Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>561346.0495131966</v>
+        <v>561326</v>
       </c>
       <c r="R12" t="n">
-        <v>6630319.707448714</v>
+        <v>6630328</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2017,27 +1828,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2020-11-05</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>inventering för Lst</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2046,43 +1842,39 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>högväxt äldre barrskog</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>nydöd tall märgborrar</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Olof Hedgren</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>95741056</v>
+        <v>132477434</v>
       </c>
       <c r="B13" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91937</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2090,33 +1882,25 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
@@ -2125,10 +1909,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>561345.6225916465</v>
+        <v>561397</v>
       </c>
       <c r="R13" t="n">
-        <v>6630284.474623516</v>
+        <v>6630622</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2155,22 +1939,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2185,7 +1959,12 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Barrblandskog, renlavshällar</t>
+          <t>Gammal barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2203,64 +1982,50 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>95741054</v>
+        <v>68993357</v>
       </c>
       <c r="B14" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4366</v>
+        <v>5966</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>561350.3632694499</v>
+        <v>561339</v>
       </c>
       <c r="R14" t="n">
-        <v>6630302.668992496</v>
+        <v>6630339</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2284,27 +2049,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-01-07</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2021-08-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 fruktkropp</t>
+          <t>2018-01-07</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2317,57 +2067,47 @@
       <c r="AG14" t="b">
         <v>0</v>
       </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Barrblandskog, renlavshällar</t>
-        </is>
-      </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>103261064</v>
+        <v>112708917</v>
       </c>
       <c r="B15" t="n">
-        <v>90074</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2380,13 +2120,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>561427.9209254094</v>
+        <v>561376</v>
       </c>
       <c r="R15" t="n">
-        <v>6630642.604880042</v>
+        <v>6630523</v>
       </c>
       <c r="S15" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2410,22 +2150,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2440,12 +2170,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Granskog, dikad</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2463,43 +2188,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>103260960</v>
+        <v>112708932</v>
       </c>
       <c r="B16" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>223597</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2507,13 +2234,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>561458.2730080879</v>
+        <v>561390</v>
       </c>
       <c r="R16" t="n">
-        <v>6630696.946342558</v>
+        <v>6630592</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2537,22 +2264,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2567,7 +2284,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Skogsbilväg</t>
+          <t>Barrblandskog, renlavshällar</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2585,57 +2302,59 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103259144</v>
+        <v>120897287</v>
       </c>
       <c r="B17" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Grävlingskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>561401.2002080667</v>
+        <v>561386</v>
       </c>
       <c r="R17" t="n">
-        <v>6630704.054130085</v>
+        <v>6630526</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2659,22 +2378,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2022-08-29</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2687,82 +2406,84 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Dikad sumpskog, gran, tall, björk, klibbal</t>
+          <t>Tall/gran hällmark</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>103791244</v>
+        <v>120899831</v>
       </c>
       <c r="B18" t="n">
-        <v>8377</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>106545</v>
+        <v>5966</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>561313.9173347926</v>
+        <v>561463</v>
       </c>
       <c r="R18" t="n">
-        <v>6630495.301382116</v>
+        <v>6630396</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2786,22 +2507,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2022-09-27</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2821,7 +2532,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Gran/tallskog</t>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2839,15 +2550,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112708917</v>
+        <v>121114354</v>
       </c>
       <c r="B19" t="n">
-        <v>91080</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2872,23 +2578,29 @@
           <t>(Schaeff.) Quél.</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Acktjärnsskogen, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>561376</v>
+        <v>561426</v>
       </c>
       <c r="R19" t="n">
-        <v>6630523</v>
+        <v>6630572</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2912,12 +2624,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2926,39 +2648,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>Barrblandskog, renlavshällar</t>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>112708932</v>
+        <v>121115102</v>
       </c>
       <c r="B20" t="n">
-        <v>91080</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2993,21 +2709,19 @@
           <t>fruktkroppar</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Acktjärnsskogen, Grävlingskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>561390</v>
+        <v>561395</v>
       </c>
       <c r="R20" t="n">
-        <v>6630592</v>
+        <v>6630537</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -3031,12 +2745,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3045,80 +2769,73 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>Barrblandskog, renlavshällar</t>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112708997</v>
+        <v>68993369</v>
       </c>
       <c r="B21" t="n">
-        <v>89760</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5447</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>561326</v>
+        <v>561339</v>
       </c>
       <c r="R21" t="n">
-        <v>6630328</v>
+        <v>6630339</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3142,12 +2859,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2018-01-07</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2018-01-07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>tall</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3156,44 +2878,28 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>Barrblandskog, renlavshällar</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Gran</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Ralf Lundmark</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>112709348</v>
+        <v>131627347</v>
       </c>
       <c r="B22" t="n">
-        <v>56765</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3201,49 +2907,49 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102977</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>561351</v>
+        <v>561371</v>
       </c>
       <c r="R22" t="n">
-        <v>6630479</v>
+        <v>6630566</v>
       </c>
       <c r="S22" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3267,22 +2973,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-10-13</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>16:27</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Spillkråka har födosök i en torraka av tall</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3293,31 +3004,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118454243</v>
+        <v>131654322</v>
       </c>
       <c r="B23" t="n">
-        <v>104949</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3325,49 +3036,53 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>561324</v>
+        <v>561387</v>
       </c>
       <c r="R23" t="n">
-        <v>6630341</v>
+        <v>6630519</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3391,17 +3106,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:40</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-14</t>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>5 stänglar i frukt.</t>
+          <t>Flera lockrop och sång. Läten bekräftade via analys av inspelningen av ljudfilen i Chirpity.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3410,90 +3135,76 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>Äldre barrblandskog</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>I barrförna med tall och gran</t>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
         </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Via Pia Hagfors</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120899831</v>
+        <v>131883208</v>
       </c>
       <c r="B24" t="n">
-        <v>92008</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57972</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>561463</v>
+        <v>561389</v>
       </c>
       <c r="R24" t="n">
-        <v>6630396</v>
+        <v>6630478</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3520,12 +3231,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Födosökt i tallraka</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3534,18 +3260,12 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AH24" t="inlineStr">
         <is>
           <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3563,64 +3283,60 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>120897287</v>
+        <v>82863480</v>
       </c>
       <c r="B25" t="n">
-        <v>92008</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Grävlingskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsvägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>561386</v>
+        <v>561307</v>
       </c>
       <c r="R25" t="n">
-        <v>6630526</v>
+        <v>6630253</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3644,22 +3360,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:58</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3668,7 +3384,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3679,7 +3394,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Tall/gran hällmark</t>
+          <t>Grusväg (skogsbilväg)</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3697,62 +3412,60 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>121115102</v>
+        <v>82863515</v>
       </c>
       <c r="B26" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Grävlingskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsvägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>561395</v>
+        <v>561345</v>
       </c>
       <c r="R26" t="n">
-        <v>6630537</v>
+        <v>6630266</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3776,22 +3489,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3806,6 +3519,11 @@
       <c r="AH26" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Grusväg (skogsbilväg)</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3823,62 +3541,60 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>121114354</v>
+        <v>82863552</v>
       </c>
       <c r="B27" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5966</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
+          <t>Acktjärnsvägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>561426</v>
+        <v>561380</v>
       </c>
       <c r="R27" t="n">
-        <v>6630572</v>
+        <v>6630299</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3902,22 +3618,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2020-03-16</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3932,6 +3648,11 @@
       <c r="AH27" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Grusväg (skogsbilväg)</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3949,15 +3670,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>120901658</v>
+        <v>82863586</v>
       </c>
       <c r="B28" t="n">
-        <v>56568</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3984,14 +3700,10 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -4001,17 +3713,17 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsvägen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>561456</v>
+        <v>561386</v>
       </c>
       <c r="R28" t="n">
-        <v>6630413</v>
+        <v>6630302</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -4035,17 +3747,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2020-03-16</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Hög med spillning på häll</t>
+          <t>2020-03-16</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4064,7 +3781,7 @@
       </c>
       <c r="AI28" t="inlineStr">
         <is>
-          <t>Tallhällmark</t>
+          <t>Grusväg (skogsbilväg)</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4082,59 +3799,60 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127763280</v>
+        <v>108163235</v>
       </c>
       <c r="B29" t="n">
-        <v>92734</v>
+        <v>57141</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4361</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Grävlingsskogen, Rsmnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>561378</v>
+        <v>561282</v>
       </c>
       <c r="R29" t="n">
-        <v>6630614</v>
+        <v>6630575</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4158,12 +3876,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-08-23</t>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Betesträd, spridd spillning under</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4172,9 +3895,13 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Tall/granskog med hällar och blåbärsris</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4187,68 +3914,64 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY29" t="inlineStr"/>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131081947</v>
+        <v>108163383</v>
       </c>
       <c r="B30" t="n">
-        <v>58057</v>
+        <v>57141</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Grävlingsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>561387</v>
+        <v>561367</v>
       </c>
       <c r="R30" t="n">
-        <v>6630519</v>
+        <v>6630465</v>
       </c>
       <c r="S30" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4272,22 +3995,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>15:30</t>
+          <t>2023-04-15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2023-04-15</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Betesträd med spridd spillning under</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4302,6 +4020,11 @@
       <c r="AH30" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Tall/granskog med hällar och blåbärsris</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4315,14 +4038,18 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Finnstugeskogen, Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131081201</v>
+        <v>120901658</v>
       </c>
       <c r="B31" t="n">
-        <v>57739</v>
+        <v>57141</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4330,38 +4057,38 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102621</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4370,13 +4097,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>561387</v>
+        <v>561456</v>
       </c>
       <c r="R31" t="n">
-        <v>6630519</v>
+        <v>6630413</v>
       </c>
       <c r="S31" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4400,22 +4127,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-02-08</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:25</t>
+          <t>2024-11-05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hög med spillning på häll</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4430,6 +4152,11 @@
       <c r="AH31" t="inlineStr">
         <is>
           <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Tallhällmark</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4447,32 +4174,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131654322</v>
+        <v>131537124</v>
       </c>
       <c r="B32" t="n">
-        <v>57945</v>
+        <v>57162</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4481,30 +4208,34 @@
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>passiv ljudinspelning</t>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>561387</v>
+        <v>561475</v>
       </c>
       <c r="R32" t="n">
-        <v>6630519</v>
+        <v>6630442</v>
       </c>
       <c r="S32" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4528,27 +4259,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Flera lockrop och sång. Läten bekräftade via analys av inspelningen av ljudfilen i Chirpity.</t>
+          <t>Spridd spillning under tall, betesträd</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4559,11 +4290,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4573,34 +4299,38 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Via Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131678761</v>
+        <v>131881710</v>
       </c>
       <c r="B33" t="n">
-        <v>58077</v>
+        <v>57162</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>103035</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Corvus corone</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4608,36 +4338,30 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>passiv ljudinspelning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>561387</v>
+        <v>561376</v>
       </c>
       <c r="R33" t="n">
-        <v>6630519</v>
+        <v>6630304</v>
       </c>
       <c r="S33" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4661,22 +4385,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>16:23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På grusväg</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4687,11 +4416,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4701,17 +4425,17 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Via Pia Hagfors</t>
+          <t>Pia Hagfors</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131537124</v>
+        <v>131881765</v>
       </c>
       <c r="B34" t="n">
-        <v>57136</v>
+        <v>57162</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4736,11 +4460,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
@@ -4752,24 +4472,20 @@
           <t>färsk spillning</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>561475</v>
+        <v>561373</v>
       </c>
       <c r="R34" t="n">
-        <v>6630442</v>
+        <v>6630297</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4793,27 +4509,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Spridd spillning under tall, betesträd</t>
+          <t>På grusväg</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4844,60 +4560,60 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131627347</v>
+        <v>131883389</v>
       </c>
       <c r="B35" t="n">
-        <v>57945</v>
+        <v>57162</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>561371</v>
+        <v>561386</v>
       </c>
       <c r="R35" t="n">
-        <v>6630566</v>
+        <v>6630312</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4921,27 +4637,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:27</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillkråka har födosök i en torraka av tall</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4952,11 +4663,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4969,14 +4675,18 @@
           <t>Pia Hagfors</t>
         </is>
       </c>
-      <c r="AY35" t="inlineStr"/>
+      <c r="AY35" t="inlineStr">
+        <is>
+          <t>Skogsprojektet</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131883389</v>
+        <v>132477950</v>
       </c>
       <c r="B36" t="n">
-        <v>57141</v>
+        <v>57162</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -5005,7 +4715,7 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>hona</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -5016,17 +4726,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
+          <t>Grävlingsskogen, Vstm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>561386</v>
+        <v>561288</v>
       </c>
       <c r="R36" t="n">
-        <v>6630312</v>
+        <v>6630451</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -5050,22 +4760,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>17:38</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>17:38</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5076,30 +4776,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Barrblandskog, hällmarker</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Tom Sävström</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>Skogsprojektet</t>
-        </is>
-      </c>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131881710</v>
+        <v>89542211</v>
       </c>
       <c r="B37" t="n">
-        <v>57141</v>
+        <v>4775</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5107,47 +4808,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>100299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
+          <t>N om Stora Acktjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>561376</v>
+        <v>561435</v>
       </c>
       <c r="R37" t="n">
-        <v>6630304</v>
+        <v>6630445</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -5171,27 +4867,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:23</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>På grusväg</t>
+          <t>inventering för Lst</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5202,72 +4888,79 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>högväxt äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>torrgran</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131883208</v>
+        <v>89542212</v>
       </c>
       <c r="B38" t="n">
-        <v>57950</v>
+        <v>5179</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Acktjärnsskogen, Ramnäs, Vstm , Acktjärnsskogen, Ramnäs, Vstm , Vstm</t>
+          <t>N om Stora Acktjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>561389</v>
+        <v>561435</v>
       </c>
       <c r="R38" t="n">
-        <v>6630478</v>
+        <v>6630445</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5291,27 +4984,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>17:30</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Födosökt i tallraka</t>
+          <t>inventering för Lst</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5323,68 +5006,79 @@
       <c r="AG38" t="b">
         <v>0</v>
       </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>högväxt äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>torrgran</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Pia Hagfors</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>132477434</v>
+        <v>89542200</v>
       </c>
       <c r="B39" t="n">
-        <v>91881</v>
+        <v>9113</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>101603</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Furustumpbagge</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Plegaderus saucius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
+          <t>Erichson, 1834</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>N om Stora Acktjärnen, Vstm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>561397</v>
+        <v>561346</v>
       </c>
       <c r="R39" t="n">
-        <v>6630622</v>
+        <v>6630320</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5411,12 +5105,17 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2020-11-05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>inventering för Lst</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5425,39 +5124,38 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
       <c r="AI39" t="inlineStr">
         <is>
-          <t>Gammal barrblandskog</t>
+          <t>högväxt äldre barrskog</t>
         </is>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>nydöd tall märgborrar</t>
         </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Tom Sävström</t>
+          <t>Olof Hedgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>132477950</v>
+        <v>101343603</v>
       </c>
       <c r="B40" t="n">
-        <v>57145</v>
+        <v>57754</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5465,16 +5163,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>102118</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5482,32 +5180,36 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Grävlingsskogen, Vstm</t>
+          <t>Acktjärnsskogen, Ramnäs, Vstm, Vstm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>561288</v>
+        <v>561425</v>
       </c>
       <c r="R40" t="n">
-        <v>6630451</v>
+        <v>6630405</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5531,12 +5233,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>01:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2022-06-02</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>01:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5547,24 +5259,2898 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AI40" t="inlineStr">
-        <is>
-          <t>Barrblandskog, hällmarker</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131081201</v>
+      </c>
+      <c r="B41" t="n">
+        <v>57794</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S41" t="n">
+        <v>50</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>112709348</v>
+      </c>
+      <c r="B42" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>561351</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6630479</v>
+      </c>
+      <c r="S42" t="n">
+        <v>100</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
+      <c r="AX42" t="inlineStr">
         <is>
           <t>Tom Sävström</t>
         </is>
       </c>
-      <c r="AY40" t="inlineStr"/>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>127759021</v>
+      </c>
+      <c r="B43" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Acktjärnsvägen, Ramnäs, Vstm, Acktjärnsvägen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>561466</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6630720</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-08-23</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Vid vägkanten, lyfte när jag kom med bil. Flög västerut.</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Öppen fastmark - med eller utan enstaka träd</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131678718</v>
+      </c>
+      <c r="B44" t="n">
+        <v>58250</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S44" t="n">
+        <v>100</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Via Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131081947</v>
+      </c>
+      <c r="B45" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S45" t="n">
+        <v>50</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-02-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131678732</v>
+      </c>
+      <c r="B46" t="n">
+        <v>58131</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S46" t="n">
+        <v>100</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Via Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131678761</v>
+      </c>
+      <c r="B47" t="n">
+        <v>58104</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>103035</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Kråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Corvus corone</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>passiv ljudinspelning</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>561387</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6630519</v>
+      </c>
+      <c r="S47" t="n">
+        <v>100</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Via Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>89542208</v>
+      </c>
+      <c r="B48" t="n">
+        <v>5004</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>105212</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Barrpraktbagge</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Chrysobothris chrysostigma</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>N om Stora Acktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>561321</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6630426</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>inventering för Lst</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="inlineStr">
+        <is>
+          <t>högväxt äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>bruten solexponerad granstam</t>
+        </is>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>89542203</v>
+      </c>
+      <c r="B49" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>N om Stora Acktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>561346</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6630320</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>inventering för Lst</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="inlineStr">
+        <is>
+          <t>högväxt äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>nydöd tall</t>
+        </is>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>89542206</v>
+      </c>
+      <c r="B50" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>N om Stora Acktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>561354</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6630380</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>inventering för Lst</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="inlineStr">
+        <is>
+          <t>högväxt äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>grov torraka</t>
+        </is>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>89542209</v>
+      </c>
+      <c r="B51" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>N om Stora Acktjärnen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>561332</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6630563</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2020-11-05</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>inventering för Lst</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="inlineStr">
+        <is>
+          <t>högväxt äldre barrskog</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>torrtall</t>
+        </is>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Olof Hedgren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>103791244</v>
+      </c>
+      <c r="B52" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Ramnäs, Vstm, Vstm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>561314</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6630495</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2022-09-27</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="inlineStr"/>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>Gran/tallskog</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Pia Hagfors</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>118454243</v>
+      </c>
+      <c r="B53" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>561324</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6630341</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-07-14</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>5 stänglar i frukt.</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="inlineStr">
+        <is>
+          <t>Äldre barrblandskog</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>I barrförna med tall och gran</t>
+        </is>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>103259144</v>
+      </c>
+      <c r="B54" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>561401</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6630704</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF54" t="inlineStr"/>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>Dikad sumpskog, gran, tall, björk, klibbal</t>
+        </is>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>103259210</v>
+      </c>
+      <c r="B55" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>561410</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6630745</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF55" t="inlineStr"/>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>Dikad sumpskog, gran, tall, björk, klibbal</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>112709094</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>561542</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6630568</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI56" t="inlineStr">
+        <is>
+          <t>Gammal dikad barrblandskog</t>
+        </is>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>112709171</v>
+      </c>
+      <c r="B57" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>561550</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6630588</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI57" t="inlineStr">
+        <is>
+          <t>Gräns gammal barrblandskog, trädbevuxen mosse</t>
+        </is>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>112709328</v>
+      </c>
+      <c r="B58" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>561512</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6630666</v>
+      </c>
+      <c r="S58" t="n">
+        <v>25</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2023-10-13</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF58" t="inlineStr"/>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI58" t="inlineStr">
+        <is>
+          <t>Trädbevuxen mosse</t>
+        </is>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>103259204</v>
+      </c>
+      <c r="B59" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>561410</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6630745</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF59" t="inlineStr"/>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI59" t="inlineStr">
+        <is>
+          <t>Dikad sumpskog, gran, tall, björk, klibbal</t>
+        </is>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>103260814</v>
+      </c>
+      <c r="B60" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>561398</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6630769</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF60" t="inlineStr"/>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>103261132</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>561482</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6630524</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF61" t="inlineStr"/>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI61" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>103261149</v>
+      </c>
+      <c r="B62" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>561478</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6630326</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF62" t="inlineStr"/>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI62" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>103261171</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>561419</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6630301</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI63" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>103260809</v>
+      </c>
+      <c r="B64" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>561398</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6630769</v>
+      </c>
+      <c r="S64" t="n">
+        <v>25</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI64" t="inlineStr">
+        <is>
+          <t>Sumpskog</t>
+        </is>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>103260960</v>
+      </c>
+      <c r="B65" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="N65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Grävlingsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>561458</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6630697</v>
+      </c>
+      <c r="S65" t="n">
+        <v>25</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Ramnäs</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2022-08-29</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF65" t="inlineStr"/>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="inlineStr">
+        <is>
+          <t>Skogsbilväg</t>
+        </is>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 46468-2024 artfynd.xlsx
+++ b/artfynd/A 46468-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY65"/>
+  <dimension ref="A1:AZ65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477399</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261064</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127763280</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1103,6 +1123,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68993358</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95741056</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1336,6 +1366,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95741054</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1442,6 +1477,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261122</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261193</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1650,6 +1695,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1282521</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1757,6 +1807,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1677130</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1868,6 +1923,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112708997</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1979,6 +2039,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477434</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2079,6 +2144,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68993357</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2185,6 +2255,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112708917</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2299,6 +2374,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112708932</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2428,6 +2508,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120897287</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2547,6 +2632,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120899831</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2668,6 +2758,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121114354</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2789,6 +2884,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121115102</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2893,6 +2993,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/68993369</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3022,6 +3127,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131627347</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3155,6 +3265,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131654322</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3280,6 +3395,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883208</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3409,6 +3529,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82863480</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3538,6 +3663,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82863515</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3667,6 +3797,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82863552</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3796,6 +3931,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82863586</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3919,6 +4059,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108163235</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4043,6 +4188,11 @@
           <t>Naturvärdesinventering Finnstugeskogen, Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108163383</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4171,6 +4321,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120901658</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4307,6 +4462,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131537124</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4429,6 +4589,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131881710</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4557,6 +4722,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131881765</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4680,6 +4850,11 @@
           <t>Skogsprojektet</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131883389</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4794,6 +4969,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132477950</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4911,6 +5091,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542211</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5028,6 +5213,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542212</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5149,6 +5339,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542200</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5272,6 +5467,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101343603</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5400,6 +5600,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131081201</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5519,6 +5724,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112709348</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5645,6 +5855,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127759021</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5773,6 +5988,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131678718</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5901,6 +6121,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131081947</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6029,6 +6254,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131678732</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6157,6 +6387,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131678761</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6274,6 +6509,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542208</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6391,6 +6631,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542203</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6508,6 +6753,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542206</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6625,6 +6875,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89542209</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6742,6 +6997,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103791244</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6867,6 +7127,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118454243</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6974,6 +7239,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103259144</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7081,6 +7351,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103259210</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7188,6 +7463,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112709094</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7295,6 +7575,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112709171</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7402,6 +7687,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112709328</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7509,6 +7799,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103259204</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7616,6 +7911,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260814</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7723,6 +8023,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261132</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7830,6 +8135,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261149</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7937,6 +8247,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103261171</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8044,6 +8359,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260809</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8151,8 +8471,79 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103260960</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>